--- a/outputs/Rice_(high_quality)_tukey_classification_matrix.xlsx
+++ b/outputs/Rice_(high_quality)_tukey_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="110">
   <si>
     <t>2020 May</t>
   </si>
@@ -343,55 +343,7 @@
     <t>Minimal</t>
   </si>
   <si>
-    <t>Alert</t>
-  </si>
-  <si>
-    <t>Alarm</t>
-  </si>
-  <si>
-    <t>4%</t>
-  </si>
-  <si>
-    <t>8%</t>
-  </si>
-  <si>
-    <t>3%</t>
-  </si>
-  <si>
-    <t>1%</t>
-  </si>
-  <si>
     <t>0%</t>
-  </si>
-  <si>
-    <t>11%</t>
-  </si>
-  <si>
-    <t>13%</t>
-  </si>
-  <si>
-    <t>6%</t>
-  </si>
-  <si>
-    <t>14%</t>
-  </si>
-  <si>
-    <t>15%</t>
-  </si>
-  <si>
-    <t>7%</t>
-  </si>
-  <si>
-    <t>10%</t>
-  </si>
-  <si>
-    <t>17%</t>
-  </si>
-  <si>
-    <t>18%</t>
-  </si>
-  <si>
-    <t>20%</t>
   </si>
 </sst>
 </file>
@@ -1081,13 +1033,13 @@
         <v>108</v>
       </c>
       <c r="AA2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AB2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD2" t="s">
         <v>108</v>
@@ -1123,16 +1075,16 @@
         <v>108</v>
       </c>
       <c r="AO2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AP2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AQ2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AS2" t="s">
         <v>108</v>
@@ -1219,13 +1171,13 @@
         <v>108</v>
       </c>
       <c r="BU2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BV2" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BW2" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1308,7 +1260,7 @@
         <v>108</v>
       </c>
       <c r="AA3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AB3" t="s">
         <v>108</v>
@@ -1317,16 +1269,16 @@
         <v>108</v>
       </c>
       <c r="AD3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH3" t="s">
         <v>108</v>
@@ -1434,25 +1386,25 @@
         <v>108</v>
       </c>
       <c r="BQ3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BR3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="BV3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BW3" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1535,7 +1487,7 @@
         <v>108</v>
       </c>
       <c r="AA4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AB4" t="s">
         <v>108</v>
@@ -1544,7 +1496,7 @@
         <v>108</v>
       </c>
       <c r="AD4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AE4" t="s">
         <v>108</v>
@@ -1565,13 +1517,13 @@
         <v>108</v>
       </c>
       <c r="AK4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AN4" t="s">
         <v>108</v>
@@ -1580,7 +1532,7 @@
         <v>108</v>
       </c>
       <c r="AP4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AQ4" t="s">
         <v>108</v>
@@ -1670,16 +1622,16 @@
         <v>108</v>
       </c>
       <c r="BT4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="BV4" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="BW4" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1765,19 +1717,19 @@
         <v>108</v>
       </c>
       <c r="AB5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AC5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AD5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AE5" t="s">
         <v>108</v>
       </c>
       <c r="AF5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG5" t="s">
         <v>108</v>
@@ -1891,22 +1843,22 @@
         <v>108</v>
       </c>
       <c r="BR5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BS5" t="s">
         <v>108</v>
       </c>
       <c r="BT5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU5" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BV5" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="BW5" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1995,7 +1947,7 @@
         <v>108</v>
       </c>
       <c r="AC6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AD6" t="s">
         <v>108</v>
@@ -2031,7 +1983,7 @@
         <v>108</v>
       </c>
       <c r="AO6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP6" t="s">
         <v>108</v>
@@ -2121,19 +2073,19 @@
         <v>108</v>
       </c>
       <c r="BS6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BV6" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BW6" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2354,13 +2306,13 @@
         <v>108</v>
       </c>
       <c r="BU7" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="BV7" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="BW7" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2443,28 +2395,28 @@
         <v>108</v>
       </c>
       <c r="AA8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC8" t="s">
         <v>108</v>
       </c>
       <c r="AD8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AE8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI8" t="s">
         <v>108</v>
@@ -2476,7 +2428,7 @@
         <v>108</v>
       </c>
       <c r="AL8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM8" t="s">
         <v>108</v>
@@ -2566,28 +2518,28 @@
         <v>108</v>
       </c>
       <c r="BP8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BQ8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BR8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT8" t="s">
         <v>108</v>
       </c>
       <c r="BU8" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="BV8" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="BW8" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2796,25 +2748,25 @@
         <v>108</v>
       </c>
       <c r="BQ9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BR9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS9" t="s">
         <v>108</v>
       </c>
       <c r="BT9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU9" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="BV9" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BW9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2906,7 +2858,7 @@
         <v>108</v>
       </c>
       <c r="AD10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE10" t="s">
         <v>108</v>
@@ -2915,31 +2867,31 @@
         <v>108</v>
       </c>
       <c r="AG10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AL10" t="s">
         <v>108</v>
       </c>
       <c r="AM10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AN10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AO10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AP10" t="s">
         <v>108</v>
@@ -3023,25 +2975,25 @@
         <v>108</v>
       </c>
       <c r="BQ10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BR10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU10" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="BV10" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="BW10" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3157,7 +3109,7 @@
         <v>108</v>
       </c>
       <c r="AL11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM11" t="s">
         <v>108</v>
@@ -3253,22 +3205,22 @@
         <v>108</v>
       </c>
       <c r="BR11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU11" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BV11" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BW11" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:75">
@@ -3351,19 +3303,19 @@
         <v>108</v>
       </c>
       <c r="AA12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AC12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AD12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AE12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF12" t="s">
         <v>108</v>
@@ -3381,13 +3333,13 @@
         <v>108</v>
       </c>
       <c r="AK12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AL12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN12" t="s">
         <v>108</v>
@@ -3396,10 +3348,10 @@
         <v>108</v>
       </c>
       <c r="AP12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AQ12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AR12" t="s">
         <v>108</v>
@@ -3489,13 +3441,13 @@
         <v>108</v>
       </c>
       <c r="BU12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BV12" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="BW12" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:75">
@@ -3578,31 +3530,31 @@
         <v>108</v>
       </c>
       <c r="AA13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AB13" t="s">
         <v>108</v>
       </c>
       <c r="AC13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ13" t="s">
         <v>108</v>
@@ -3611,7 +3563,7 @@
         <v>108</v>
       </c>
       <c r="AL13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM13" t="s">
         <v>108</v>
@@ -3701,28 +3653,28 @@
         <v>108</v>
       </c>
       <c r="BP13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BQ13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BR13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU13" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="BV13" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="BW13" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:75">
@@ -3937,19 +3889,19 @@
         <v>108</v>
       </c>
       <c r="BS14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU14" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="BV14" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="BW14" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:75">
@@ -4035,7 +3987,7 @@
         <v>108</v>
       </c>
       <c r="AB15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AC15" t="s">
         <v>108</v>
@@ -4062,7 +4014,7 @@
         <v>108</v>
       </c>
       <c r="AK15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL15" t="s">
         <v>108</v>
@@ -4164,19 +4116,19 @@
         <v>108</v>
       </c>
       <c r="BS15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BT15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU15" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="BV15" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="BW15" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:75">
@@ -4262,25 +4214,25 @@
         <v>108</v>
       </c>
       <c r="AB16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AC16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AE16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI16" t="s">
         <v>108</v>
@@ -4385,7 +4337,7 @@
         <v>108</v>
       </c>
       <c r="BQ16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BR16" t="s">
         <v>108</v>
@@ -4397,13 +4349,13 @@
         <v>108</v>
       </c>
       <c r="BU16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BV16" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="BW16" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:75">
@@ -4510,16 +4462,16 @@
         <v>108</v>
       </c>
       <c r="AI17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AJ17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM17" t="s">
         <v>108</v>
@@ -4612,25 +4564,25 @@
         <v>108</v>
       </c>
       <c r="BQ17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BR17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT17" t="s">
         <v>108</v>
       </c>
       <c r="BU17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BV17" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BW17" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:75">
@@ -4713,19 +4665,19 @@
         <v>108</v>
       </c>
       <c r="AA18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AC18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF18" t="s">
         <v>108</v>
@@ -4737,22 +4689,22 @@
         <v>108</v>
       </c>
       <c r="AI18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AJ18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK18" t="s">
         <v>108</v>
       </c>
       <c r="AL18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM18" t="s">
         <v>108</v>
       </c>
       <c r="AN18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO18" t="s">
         <v>108</v>
@@ -4839,7 +4791,7 @@
         <v>108</v>
       </c>
       <c r="BQ18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BR18" t="s">
         <v>108</v>
@@ -4848,16 +4800,16 @@
         <v>108</v>
       </c>
       <c r="BT18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU18" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="BV18" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="BW18" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:75">
@@ -5069,22 +5021,22 @@
         <v>108</v>
       </c>
       <c r="BR19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BV19" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="BW19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:75">
@@ -5167,7 +5119,7 @@
         <v>108</v>
       </c>
       <c r="AA20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AB20" t="s">
         <v>108</v>
@@ -5200,7 +5152,7 @@
         <v>108</v>
       </c>
       <c r="AL20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM20" t="s">
         <v>108</v>
@@ -5299,19 +5251,19 @@
         <v>108</v>
       </c>
       <c r="BS20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BT20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU20" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BV20" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BW20" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:75">
@@ -5397,13 +5349,13 @@
         <v>108</v>
       </c>
       <c r="AB21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AD21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE21" t="s">
         <v>108</v>
@@ -5427,16 +5379,16 @@
         <v>108</v>
       </c>
       <c r="AL21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP21" t="s">
         <v>108</v>
@@ -5523,22 +5475,22 @@
         <v>108</v>
       </c>
       <c r="BR21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU21" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="BV21" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BW21" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:75">
@@ -5624,10 +5576,10 @@
         <v>108</v>
       </c>
       <c r="AB22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD22" t="s">
         <v>108</v>
@@ -5648,16 +5600,16 @@
         <v>108</v>
       </c>
       <c r="AJ22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AN22" t="s">
         <v>108</v>
@@ -5756,16 +5708,16 @@
         <v>108</v>
       </c>
       <c r="BT22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BU22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BV22" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BW22" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:75">
@@ -5857,7 +5809,7 @@
         <v>108</v>
       </c>
       <c r="AD23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AE23" t="s">
         <v>108</v>
@@ -5869,13 +5821,13 @@
         <v>108</v>
       </c>
       <c r="AH23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AJ23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK23" t="s">
         <v>108</v>
@@ -5974,25 +5926,25 @@
         <v>108</v>
       </c>
       <c r="BQ23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BR23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU23" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BV23" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BW23" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:75">
@@ -6204,22 +6156,22 @@
         <v>108</v>
       </c>
       <c r="BR24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU24" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BV24" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="BW24" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:75">
@@ -6302,16 +6254,16 @@
         <v>108</v>
       </c>
       <c r="AA25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AD25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AE25" t="s">
         <v>108</v>
@@ -6320,22 +6272,22 @@
         <v>108</v>
       </c>
       <c r="AG25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ25" t="s">
         <v>108</v>
       </c>
       <c r="AK25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AL25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM25" t="s">
         <v>108</v>
@@ -6428,25 +6380,25 @@
         <v>108</v>
       </c>
       <c r="BQ25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BR25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU25" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="BV25" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BW25" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:75">
@@ -6667,13 +6619,13 @@
         <v>108</v>
       </c>
       <c r="BU26" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="BV26" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="BW26" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:75">
@@ -6762,37 +6714,37 @@
         <v>108</v>
       </c>
       <c r="AC27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AD27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE27" t="s">
         <v>108</v>
       </c>
       <c r="AF27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH27" t="s">
         <v>108</v>
       </c>
       <c r="AI27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AJ27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN27" t="s">
         <v>108</v>
@@ -6894,13 +6846,13 @@
         <v>108</v>
       </c>
       <c r="BU27" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="BV27" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BW27" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:75">
@@ -6983,13 +6935,13 @@
         <v>108</v>
       </c>
       <c r="AA28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AB28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD28" t="s">
         <v>108</v>
@@ -7013,13 +6965,13 @@
         <v>108</v>
       </c>
       <c r="AK28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AL28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN28" t="s">
         <v>108</v>
@@ -7121,13 +7073,13 @@
         <v>108</v>
       </c>
       <c r="BU28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BV28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BW28" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:75">
@@ -7222,7 +7174,7 @@
         <v>108</v>
       </c>
       <c r="AE29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF29" t="s">
         <v>108</v>
@@ -7231,19 +7183,19 @@
         <v>108</v>
       </c>
       <c r="AH29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AJ29" t="s">
         <v>108</v>
       </c>
       <c r="AK29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM29" t="s">
         <v>108</v>
@@ -7252,7 +7204,7 @@
         <v>108</v>
       </c>
       <c r="AO29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AP29" t="s">
         <v>108</v>
@@ -7336,25 +7288,25 @@
         <v>108</v>
       </c>
       <c r="BQ29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BR29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BT29" t="s">
         <v>108</v>
       </c>
       <c r="BU29" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BV29" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="BW29" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" spans="1:75">
@@ -7467,13 +7419,13 @@
         <v>108</v>
       </c>
       <c r="AK30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AL30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN30" t="s">
         <v>108</v>
@@ -7563,25 +7515,25 @@
         <v>108</v>
       </c>
       <c r="BQ30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BR30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BT30" t="s">
         <v>108</v>
       </c>
       <c r="BU30" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BV30" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BW30" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" spans="1:75">
@@ -7667,10 +7619,10 @@
         <v>108</v>
       </c>
       <c r="AB31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AC31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AD31" t="s">
         <v>108</v>
@@ -7793,22 +7745,22 @@
         <v>108</v>
       </c>
       <c r="BR31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU31" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BV31" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="BW31" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="32" spans="1:75">
@@ -7885,34 +7837,34 @@
         <v>108</v>
       </c>
       <c r="Y32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Z32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI32" t="s">
         <v>108</v>
@@ -8017,25 +7969,25 @@
         <v>108</v>
       </c>
       <c r="BQ32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BR32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU32" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="BV32" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="BW32" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
     </row>
     <row r="33" spans="1:75">
@@ -8118,19 +8070,19 @@
         <v>108</v>
       </c>
       <c r="AA33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF33" t="s">
         <v>108</v>
@@ -8148,19 +8100,19 @@
         <v>108</v>
       </c>
       <c r="AK33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AL33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP33" t="s">
         <v>108</v>
@@ -8247,22 +8199,22 @@
         <v>108</v>
       </c>
       <c r="BR33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU33" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="BV33" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="BW33" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34" spans="1:75">
@@ -8351,10 +8303,10 @@
         <v>108</v>
       </c>
       <c r="AC34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE34" t="s">
         <v>108</v>
@@ -8372,13 +8324,13 @@
         <v>108</v>
       </c>
       <c r="AJ34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AL34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM34" t="s">
         <v>108</v>
@@ -8474,7 +8426,7 @@
         <v>108</v>
       </c>
       <c r="BR34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS34" t="s">
         <v>108</v>
@@ -8483,13 +8435,13 @@
         <v>108</v>
       </c>
       <c r="BU34" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BV34" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BW34" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Rice_(high_quality)_tukey_classification_matrix.xlsx
+++ b/outputs/Rice_(high_quality)_tukey_classification_matrix.xlsx
@@ -340,7 +340,7 @@
     <t>Zabul</t>
   </si>
   <si>
-    <t>Minimal</t>
+    <t>No concern</t>
   </si>
   <si>
     <t>0%</t>
